--- a/tabular/genus/tetra-refseqs-side-data.xlsx
+++ b/tabular/genus/tetra-refseqs-side-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNA/Parvovirus-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817E5CF1-F269-1344-8367-FC8813D461DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF39DA84-2165-2244-B3A8-987F8B858D05}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14960" yWindow="1440" windowWidth="28800" windowHeight="17540" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REFSET" sheetId="3" r:id="rId1"/>
@@ -2067,7 +2067,32 @@
     <cellStyle name="Hyperlink" xfId="913" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF660066"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <mruColors>
@@ -2085,6 +2110,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{303246E9-6F84-CA46-BFCF-ABF89D3BCF0C}" name="Table1" displayName="Table1" ref="A1:M11" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:M11" xr:uid="{85D49266-D12B-E54B-94EB-B41E825F97BE}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{D06D1858-A16E-B84A-A134-A5CE9329E379}" name="sequenceID"/>
+    <tableColumn id="2" xr3:uid="{4E7074B5-D52C-3744-BBA1-2FC0AB35232B}" name="virus_name"/>
+    <tableColumn id="3" xr3:uid="{210233E3-1666-434B-9237-3AD50C80E18E}" name="virus_full_name"/>
+    <tableColumn id="4" xr3:uid="{44F8D940-9C40-704B-BC16-B76C4C0160DE}" name="host_species"/>
+    <tableColumn id="5" xr3:uid="{D9B79E50-B600-684A-9884-01C7936A07EE}" name="assign_clade"/>
+    <tableColumn id="6" xr3:uid="{BDC7E4C6-CA3E-7D4E-B378-4C045769D9F3}" name="virus_subfamily"/>
+    <tableColumn id="7" xr3:uid="{163077D1-0F35-0D4E-B18C-0B355CD027D6}" name="virus_genus"/>
+    <tableColumn id="8" xr3:uid="{98AAA741-23A7-3040-B761-D6224C67F24C}" name="assign_subclade"/>
+    <tableColumn id="9" xr3:uid="{36D018E3-BA2E-4D47-B829-EA2AE094C318}" name="virus_clade_ns"/>
+    <tableColumn id="10" xr3:uid="{10DE9F80-433D-4649-B484-739A5F6910F3}" name="virus_subclade_ns"/>
+    <tableColumn id="11" xr3:uid="{E5E847BD-33BB-CE45-B22F-0CF40E5ADFC5}" name="virus_clade_vp"/>
+    <tableColumn id="12" xr3:uid="{17D3E459-74D2-5B48-9FAB-1DF9ACB9526F}" name="virus_subclade_vp"/>
+    <tableColumn id="13" xr3:uid="{1853289A-F08A-7842-83A8-817B424352CC}" name="lab_construct"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2418,7 +2465,7 @@
     <col min="4" max="8" width="18.6640625" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
     <col min="12" max="12" width="19.5" customWidth="1"/>
     <col min="13" max="13" width="15.33203125" customWidth="1"/>
   </cols>
@@ -2880,6 +2927,9 @@
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
